--- a/InputData/elec/FoSYCRpUNL/Frac of Start Year Cap Ret per Unit Net Loss.xlsx
+++ b/InputData/elec/FoSYCRpUNL/Frac of Start Year Cap Ret per Unit Net Loss.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\FoSYCRpUNL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\FoSYCRpUNL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30147DF2-318E-4595-911D-55FC8B05B11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D11D6C-1D75-4323-AE84-84EA22FCED8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="21600" windowHeight="12645" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{67B50A2A-83E2-40E1-A966-DC033ADD8EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,23 +34,92 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t xml:space="preserve">Sources: </t>
+  </si>
+  <si>
+    <t>(none)</t>
+  </si>
   <si>
     <t>FoSYCRpUNL Fraction of Start Year Capacity Retired per Unit Net Loss</t>
   </si>
   <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sources: </t>
-  </si>
-  <si>
-    <t>(none)</t>
-  </si>
-  <si>
     <t>This is a calibrated parameter.  It can be calibrated by aligning early-year retirements with historical retirements once other input data are in place.</t>
   </si>
   <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
+    <t>solar PV</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>offshore wind</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>Fraction of start year capacity</t>
+  </si>
+  <si>
+    <t>Unit: 1/($/(MWh))</t>
+  </si>
+  <si>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
     <t>Certain plant types are less prone to economic retirement because they are maintained for local reliability purposes.</t>
   </si>
   <si>
@@ -58,78 +127,6 @@
   </si>
   <si>
     <t>retirement fraction very low.</t>
-  </si>
-  <si>
-    <t>Unit: 1/($/(MWh))</t>
-  </si>
-  <si>
-    <t>Fraction of start year capacity</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
-    <t>solar PV</t>
-  </si>
-  <si>
-    <t>solar thermal</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>geothermal</t>
-  </si>
-  <si>
-    <t>petroleum</t>
-  </si>
-  <si>
-    <t>natural gas peaker</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>offshore wind</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>heavy or residual fuel oil</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>hard coal w CCS</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle w CCS</t>
-  </si>
-  <si>
-    <t>biomass w CCS</t>
-  </si>
-  <si>
-    <t>lignite w CCS</t>
-  </si>
-  <si>
-    <t>small modular reactor</t>
   </si>
   <si>
     <t>hydrogen combustion turbine</t>
@@ -514,44 +511,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B7A547-DAFD-4CBC-90C6-A86A1413C282}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -560,7 +554,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{498B6747-53CF-4C1D-84DD-4D89524F3F28}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
@@ -572,23 +566,23 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>1E-4</v>
@@ -596,71 +590,71 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B9">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B10">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B11">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>1E-4</v>
@@ -668,7 +662,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>1E-4</v>
@@ -676,103 +670,102 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B14">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B15">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B16">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B17">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B18">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B19">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B20">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B21">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B22">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B23">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24">
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25">
-        <f>B4</f>
-        <v>1.2500000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>